--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\2024AIDataScienceGNRClub\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D77E56-C0A4-44EF-B30E-66B0F8C83BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9688748F-DFFA-4096-B15A-BC3BF03013E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="14">
   <si>
     <t>Name</t>
   </si>
@@ -385,7 +385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -396,7 +396,7 @@
     <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -433,8 +433,11 @@
       <c r="L1" s="1">
         <v>45577</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="1">
+        <v>45584</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -471,8 +474,11 @@
       <c r="L2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -509,8 +515,11 @@
       <c r="L3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -547,8 +556,11 @@
       <c r="L4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -585,8 +597,11 @@
       <c r="L5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -623,8 +638,11 @@
       <c r="L6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -661,8 +679,11 @@
       <c r="L7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -699,8 +720,11 @@
       <c r="L8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -737,8 +761,11 @@
       <c r="L9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -773,6 +800,9 @@
         <v>13</v>
       </c>
       <c r="L10" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" t="s">
         <v>13</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9688748F-DFFA-4096-B15A-BC3BF03013E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38BF030-D8FA-4458-A72A-7F3C941A97E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="15">
   <si>
     <t>Name</t>
   </si>
@@ -63,10 +64,13 @@
     <t>Ronak Chaudhari</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>A</t>
   </si>
   <si>
-    <t>A</t>
+    <t>Total/60</t>
+  </si>
+  <si>
+    <t>Total/5</t>
   </si>
 </sst>
 </file>
@@ -466,16 +470,16 @@
         <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L2" t="s">
         <v>8</v>
       </c>
       <c r="M2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -486,7 +490,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -501,19 +505,19 @@
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M3" t="s">
         <v>8</v>
@@ -533,7 +537,7 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -545,7 +549,7 @@
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
         <v>8</v>
@@ -574,10 +578,10 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -598,7 +602,7 @@
         <v>10</v>
       </c>
       <c r="M5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -656,7 +660,7 @@
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
@@ -674,13 +678,13 @@
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L7" t="s">
         <v>8</v>
       </c>
       <c r="M7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -697,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -721,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="M8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -744,7 +748,7 @@
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -779,34 +783,644 @@
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
         <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0024F37A-C562-416B-828F-1FBDF4D4E931}">
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>45500</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45507</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45514</v>
+      </c>
+      <c r="E1" s="1">
+        <v>45521</v>
+      </c>
+      <c r="F1" s="1">
+        <v>45528</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45535</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45542</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45549</v>
+      </c>
+      <c r="J1" s="1">
+        <v>45565</v>
+      </c>
+      <c r="K1" s="1">
+        <v>45572</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45577</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45584</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f>_xlfn.IFS(Sheet1!B2="P", 5, Sheet1!B2="O", 3, Sheet1!B2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <f>_xlfn.IFS(Sheet1!C2="P", 5, Sheet1!C2="O", 3, Sheet1!C2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <f>_xlfn.IFS(Sheet1!D2="P", 5, Sheet1!D2="O", 3, Sheet1!D2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.IFS(Sheet1!E2="P", 5, Sheet1!E2="O", 3, Sheet1!E2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F2">
+        <f>_xlfn.IFS(Sheet1!F2="P", 5, Sheet1!F2="O", 3, Sheet1!F2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <f>_xlfn.IFS(Sheet1!G2="P", 5, Sheet1!G2="O", 3, Sheet1!G2="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.IFS(Sheet1!H2="P", 5, Sheet1!H2="O", 3, Sheet1!H2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.IFS(Sheet1!I2="P", 5, Sheet1!I2="O", 3, Sheet1!I2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <f>_xlfn.IFS(Sheet1!J2="P", 5, Sheet1!J2="O", 3, Sheet1!J2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>_xlfn.IFS(Sheet1!K2="P", 5, Sheet1!K2="O", 3, Sheet1!K2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>_xlfn.IFS(Sheet1!L2="P", 5, Sheet1!L2="O", 3, Sheet1!L2="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <f>_xlfn.IFS(Sheet1!M2="P", 5, Sheet1!M2="O", 3, Sheet1!M2="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <f>SUM(B2:M2)</f>
+        <v>43</v>
+      </c>
+      <c r="O2">
+        <f>ROUND(N2*5/60, 2)</f>
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <f>_xlfn.IFS(Sheet1!B3="P", 5, Sheet1!B3="O", 3, Sheet1!B3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <f>_xlfn.IFS(Sheet1!C3="P", 5, Sheet1!C3="O", 3, Sheet1!C3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>_xlfn.IFS(Sheet1!D3="P", 5, Sheet1!D3="O", 3, Sheet1!D3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.IFS(Sheet1!E3="P", 5, Sheet1!E3="O", 3, Sheet1!E3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <f>_xlfn.IFS(Sheet1!F3="P", 5, Sheet1!F3="O", 3, Sheet1!F3="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.IFS(Sheet1!G3="P", 5, Sheet1!G3="O", 3, Sheet1!G3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.IFS(Sheet1!H3="P", 5, Sheet1!H3="O", 3, Sheet1!H3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>_xlfn.IFS(Sheet1!I3="P", 5, Sheet1!I3="O", 3, Sheet1!I3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>_xlfn.IFS(Sheet1!J3="P", 5, Sheet1!J3="O", 3, Sheet1!J3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f>_xlfn.IFS(Sheet1!K3="P", 5, Sheet1!K3="O", 3, Sheet1!K3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>_xlfn.IFS(Sheet1!L3="P", 5, Sheet1!L3="O", 3, Sheet1!L3="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>_xlfn.IFS(Sheet1!M3="P", 5, Sheet1!M3="O", 3, Sheet1!M3="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N10" si="0">SUM(B3:M3)</f>
+        <v>28</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O10" si="1">ROUND(N3*5/60, 2)</f>
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <f>_xlfn.IFS(Sheet1!B4="P", 5, Sheet1!B4="O", 3, Sheet1!B4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <f>_xlfn.IFS(Sheet1!C4="P", 5, Sheet1!C4="O", 3, Sheet1!C4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <f>_xlfn.IFS(Sheet1!D4="P", 5, Sheet1!D4="O", 3, Sheet1!D4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.IFS(Sheet1!E4="P", 5, Sheet1!E4="O", 3, Sheet1!E4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>_xlfn.IFS(Sheet1!F4="P", 5, Sheet1!F4="O", 3, Sheet1!F4="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <f>_xlfn.IFS(Sheet1!G4="P", 5, Sheet1!G4="O", 3, Sheet1!G4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.IFS(Sheet1!H4="P", 5, Sheet1!H4="O", 3, Sheet1!H4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.IFS(Sheet1!I4="P", 5, Sheet1!I4="O", 3, Sheet1!I4="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>_xlfn.IFS(Sheet1!J4="P", 5, Sheet1!J4="O", 3, Sheet1!J4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <f>_xlfn.IFS(Sheet1!K4="P", 5, Sheet1!K4="O", 3, Sheet1!K4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <f>_xlfn.IFS(Sheet1!L4="P", 5, Sheet1!L4="O", 3, Sheet1!L4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <f>_xlfn.IFS(Sheet1!M4="P", 5, Sheet1!M4="O", 3, Sheet1!M4="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <f>_xlfn.IFS(Sheet1!B5="P", 5, Sheet1!B5="O", 3, Sheet1!B5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <f>_xlfn.IFS(Sheet1!C5="P", 5, Sheet1!C5="O", 3, Sheet1!C5="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D5">
+        <f>_xlfn.IFS(Sheet1!D5="P", 5, Sheet1!D5="O", 3, Sheet1!D5="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <f>_xlfn.IFS(Sheet1!E5="P", 5, Sheet1!E5="O", 3, Sheet1!E5="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>_xlfn.IFS(Sheet1!F5="P", 5, Sheet1!F5="O", 3, Sheet1!F5="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>_xlfn.IFS(Sheet1!G5="P", 5, Sheet1!G5="O", 3, Sheet1!G5="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="H5">
+        <f>_xlfn.IFS(Sheet1!H5="P", 5, Sheet1!H5="O", 3, Sheet1!H5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <f>_xlfn.IFS(Sheet1!I5="P", 5, Sheet1!I5="O", 3, Sheet1!I5="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <f>_xlfn.IFS(Sheet1!J5="P", 5, Sheet1!J5="O", 3, Sheet1!J5="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <f>_xlfn.IFS(Sheet1!K5="P", 5, Sheet1!K5="O", 3, Sheet1!K5="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L5">
+        <f>_xlfn.IFS(Sheet1!L5="P", 5, Sheet1!L5="O", 3, Sheet1!L5="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <f>_xlfn.IFS(Sheet1!M5="P", 5, Sheet1!M5="O", 3, Sheet1!M5="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="1"/>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <f>_xlfn.IFS(Sheet1!B6="P", 5, Sheet1!B6="O", 3, Sheet1!B6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f>_xlfn.IFS(Sheet1!C6="P", 5, Sheet1!C6="O", 3, Sheet1!C6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <f>_xlfn.IFS(Sheet1!D6="P", 5, Sheet1!D6="O", 3, Sheet1!D6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <f>_xlfn.IFS(Sheet1!E6="P", 5, Sheet1!E6="O", 3, Sheet1!E6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.IFS(Sheet1!F6="P", 5, Sheet1!F6="O", 3, Sheet1!F6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <f>_xlfn.IFS(Sheet1!G6="P", 5, Sheet1!G6="O", 3, Sheet1!G6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <f>_xlfn.IFS(Sheet1!H6="P", 5, Sheet1!H6="O", 3, Sheet1!H6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I6">
+        <f>_xlfn.IFS(Sheet1!I6="P", 5, Sheet1!I6="O", 3, Sheet1!I6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <f>_xlfn.IFS(Sheet1!J6="P", 5, Sheet1!J6="O", 3, Sheet1!J6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <f>_xlfn.IFS(Sheet1!K6="P", 5, Sheet1!K6="O", 3, Sheet1!K6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <f>_xlfn.IFS(Sheet1!L6="P", 5, Sheet1!L6="O", 3, Sheet1!L6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <f>_xlfn.IFS(Sheet1!M6="P", 5, Sheet1!M6="O", 3, Sheet1!M6="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <f>_xlfn.IFS(Sheet1!B7="P", 5, Sheet1!B7="O", 3, Sheet1!B7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <f>_xlfn.IFS(Sheet1!C7="P", 5, Sheet1!C7="O", 3, Sheet1!C7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <f>_xlfn.IFS(Sheet1!D7="P", 5, Sheet1!D7="O", 3, Sheet1!D7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <f>_xlfn.IFS(Sheet1!E7="P", 5, Sheet1!E7="O", 3, Sheet1!E7="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>_xlfn.IFS(Sheet1!F7="P", 5, Sheet1!F7="O", 3, Sheet1!F7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <f>_xlfn.IFS(Sheet1!G7="P", 5, Sheet1!G7="O", 3, Sheet1!G7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <f>_xlfn.IFS(Sheet1!H7="P", 5, Sheet1!H7="O", 3, Sheet1!H7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <f>_xlfn.IFS(Sheet1!I7="P", 5, Sheet1!I7="O", 3, Sheet1!I7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <f>_xlfn.IFS(Sheet1!J7="P", 5, Sheet1!J7="O", 3, Sheet1!J7="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="K7">
+        <f>_xlfn.IFS(Sheet1!K7="P", 5, Sheet1!K7="O", 3, Sheet1!K7="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f>_xlfn.IFS(Sheet1!L7="P", 5, Sheet1!L7="O", 3, Sheet1!L7="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <f>_xlfn.IFS(Sheet1!M7="P", 5, Sheet1!M7="O", 3, Sheet1!M7="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="1"/>
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <f>_xlfn.IFS(Sheet1!B8="P", 5, Sheet1!B8="O", 3, Sheet1!B8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <f>_xlfn.IFS(Sheet1!C8="P", 5, Sheet1!C8="O", 3, Sheet1!C8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <f>_xlfn.IFS(Sheet1!D8="P", 5, Sheet1!D8="O", 3, Sheet1!D8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <f>_xlfn.IFS(Sheet1!E8="P", 5, Sheet1!E8="O", 3, Sheet1!E8="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f>_xlfn.IFS(Sheet1!F8="P", 5, Sheet1!F8="O", 3, Sheet1!F8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <f>_xlfn.IFS(Sheet1!G8="P", 5, Sheet1!G8="O", 3, Sheet1!G8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <f>_xlfn.IFS(Sheet1!H8="P", 5, Sheet1!H8="O", 3, Sheet1!H8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <f>_xlfn.IFS(Sheet1!I8="P", 5, Sheet1!I8="O", 3, Sheet1!I8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <f>_xlfn.IFS(Sheet1!J8="P", 5, Sheet1!J8="O", 3, Sheet1!J8="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="K8">
+        <f>_xlfn.IFS(Sheet1!K8="P", 5, Sheet1!K8="O", 3, Sheet1!K8="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L8">
+        <f>_xlfn.IFS(Sheet1!L8="P", 5, Sheet1!L8="O", 3, Sheet1!L8="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <f>_xlfn.IFS(Sheet1!M8="P", 5, Sheet1!M8="O", 3, Sheet1!M8="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="1"/>
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <f>_xlfn.IFS(Sheet1!B9="P", 5, Sheet1!B9="O", 3, Sheet1!B9="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <f>_xlfn.IFS(Sheet1!C9="P", 5, Sheet1!C9="O", 3, Sheet1!C9="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <f>_xlfn.IFS(Sheet1!D9="P", 5, Sheet1!D9="O", 3, Sheet1!D9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <f>_xlfn.IFS(Sheet1!E9="P", 5, Sheet1!E9="O", 3, Sheet1!E9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <f>_xlfn.IFS(Sheet1!F9="P", 5, Sheet1!F9="O", 3, Sheet1!F9="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <f>_xlfn.IFS(Sheet1!G9="P", 5, Sheet1!G9="O", 3, Sheet1!G9="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f>_xlfn.IFS(Sheet1!H9="P", 5, Sheet1!H9="O", 3, Sheet1!H9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <f>_xlfn.IFS(Sheet1!I9="P", 5, Sheet1!I9="O", 3, Sheet1!I9="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <f>_xlfn.IFS(Sheet1!J9="P", 5, Sheet1!J9="O", 3, Sheet1!J9="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <f>_xlfn.IFS(Sheet1!K9="P", 5, Sheet1!K9="O", 3, Sheet1!K9="A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="L9">
+        <f>_xlfn.IFS(Sheet1!L9="P", 5, Sheet1!L9="O", 3, Sheet1!L9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <f>_xlfn.IFS(Sheet1!M9="P", 5, Sheet1!M9="O", 3, Sheet1!M9="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="1"/>
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <f>_xlfn.IFS(Sheet1!B10="P", 5, Sheet1!B10="O", 3, Sheet1!B10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f>_xlfn.IFS(Sheet1!C10="P", 5, Sheet1!C10="O", 3, Sheet1!C10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <f>_xlfn.IFS(Sheet1!D10="P", 5, Sheet1!D10="O", 3, Sheet1!D10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <f>_xlfn.IFS(Sheet1!E10="P", 5, Sheet1!E10="O", 3, Sheet1!E10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f>_xlfn.IFS(Sheet1!F10="P", 5, Sheet1!F10="O", 3, Sheet1!F10="A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <f>_xlfn.IFS(Sheet1!G10="P", 5, Sheet1!G10="O", 3, Sheet1!G10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <f>_xlfn.IFS(Sheet1!H10="P", 5, Sheet1!H10="O", 3, Sheet1!H10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f>_xlfn.IFS(Sheet1!I10="P", 5, Sheet1!I10="O", 3, Sheet1!I10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f>_xlfn.IFS(Sheet1!J10="P", 5, Sheet1!J10="O", 3, Sheet1!J10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f>_xlfn.IFS(Sheet1!K10="P", 5, Sheet1!K10="O", 3, Sheet1!K10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f>_xlfn.IFS(Sheet1!L10="P", 5, Sheet1!L10="O", 3, Sheet1!L10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f>_xlfn.IFS(Sheet1!M10="P", 5, Sheet1!M10="O", 3, Sheet1!M10="A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="1"/>
+        <v>1.25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C38BF030-D8FA-4458-A72A-7F3C941A97E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50234C4A-D89B-4BC2-B7BA-F1CE282C6B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="16">
   <si>
     <t>Name</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Total/5</t>
+  </si>
+  <si>
+    <t>Dhruvi</t>
   </si>
 </sst>
 </file>
@@ -389,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -400,7 +403,7 @@
     <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,8 +443,11 @@
       <c r="M1" s="1">
         <v>45584</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="1">
+        <v>45591</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -481,8 +487,11 @@
       <c r="M2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -522,8 +531,11 @@
       <c r="M3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -563,8 +575,11 @@
       <c r="M4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -604,8 +619,11 @@
       <c r="M5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -645,8 +663,11 @@
       <c r="M6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -686,8 +707,11 @@
       <c r="M7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -727,8 +751,11 @@
       <c r="M8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -768,8 +795,11 @@
       <c r="M9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -808,6 +838,17 @@
       </c>
       <c r="M10" t="s">
         <v>12</v>
+      </c>
+      <c r="N10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50234C4A-D89B-4BC2-B7BA-F1CE282C6B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2507D90-92D6-40D3-8CD7-364B56AE6E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="16">
   <si>
     <t>Name</t>
   </si>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -403,7 +403,7 @@
     <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,8 +446,11 @@
       <c r="N1" s="1">
         <v>45591</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O1" s="1">
+        <v>45605</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -490,8 +493,11 @@
       <c r="N2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -534,8 +540,11 @@
       <c r="N3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -578,8 +587,11 @@
       <c r="N4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -622,8 +634,11 @@
       <c r="N5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -666,8 +681,11 @@
       <c r="N6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -710,8 +728,11 @@
       <c r="N7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -754,8 +775,11 @@
       <c r="N8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -798,8 +822,11 @@
       <c r="N9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -842,12 +869,18 @@
       <c r="N10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="O10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="N11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O11" t="s">
         <v>10</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2507D90-92D6-40D3-8CD7-364B56AE6E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321CABB2-3C6A-4051-A85C-FCBE923E196D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="16">
   <si>
     <t>Name</t>
   </si>
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -403,7 +403,7 @@
     <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,8 +449,11 @@
       <c r="O1" s="1">
         <v>45605</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="1">
+        <v>45612</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -496,8 +499,11 @@
       <c r="O2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -543,8 +549,11 @@
       <c r="O3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -590,8 +599,11 @@
       <c r="O4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -637,8 +649,11 @@
       <c r="O5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -684,8 +699,11 @@
       <c r="O6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -731,8 +749,11 @@
       <c r="O7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -778,8 +799,11 @@
       <c r="O8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -825,8 +849,11 @@
       <c r="O9" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -872,16 +899,22 @@
       <c r="O10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="N11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O11" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="P11" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321CABB2-3C6A-4051-A85C-FCBE923E196D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D095CB3B-396F-463D-AEAA-E41B0B4FAAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Dhruvi</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Gandhinagar</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
   </si>
 </sst>
 </file>
@@ -392,73 +401,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="1">
         <v>45500</v>
       </c>
-      <c r="C1" s="1">
+      <c r="D1" s="1">
         <v>45507</v>
       </c>
-      <c r="D1" s="1">
+      <c r="E1" s="1">
         <v>45514</v>
       </c>
-      <c r="E1" s="1">
+      <c r="F1" s="1">
         <v>45521</v>
       </c>
-      <c r="F1" s="1">
+      <c r="G1" s="1">
         <v>45528</v>
       </c>
-      <c r="G1" s="1">
+      <c r="H1" s="1">
         <v>45535</v>
       </c>
-      <c r="H1" s="1">
+      <c r="I1" s="1">
         <v>45542</v>
       </c>
-      <c r="I1" s="1">
+      <c r="J1" s="1">
         <v>45549</v>
       </c>
-      <c r="J1" s="1">
+      <c r="K1" s="1">
         <v>45565</v>
       </c>
-      <c r="K1" s="1">
+      <c r="L1" s="1">
         <v>45572</v>
       </c>
-      <c r="L1" s="1">
+      <c r="M1" s="1">
         <v>45577</v>
       </c>
-      <c r="M1" s="1">
+      <c r="N1" s="1">
         <v>45584</v>
       </c>
-      <c r="N1" s="1">
+      <c r="O1" s="1">
         <v>45591</v>
       </c>
-      <c r="O1" s="1">
+      <c r="P1" s="1">
         <v>45605</v>
       </c>
-      <c r="P1" s="1">
+      <c r="Q1" s="1">
         <v>45612</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R1" s="1">
+        <v>45626</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -473,60 +489,66 @@
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K2" t="s">
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O2" t="s">
         <v>8</v>
       </c>
       <c r="P2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I3" t="s">
         <v>12</v>
@@ -541,24 +563,30 @@
         <v>12</v>
       </c>
       <c r="M3" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>10</v>
+      </c>
+      <c r="R3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -567,22 +595,22 @@
         <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
         <v>8</v>
@@ -602,37 +630,43 @@
       <c r="P4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" t="s">
         <v>8</v>
       </c>
       <c r="J5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" t="s">
         <v>10</v>
@@ -641,24 +675,30 @@
         <v>10</v>
       </c>
       <c r="M5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N5" t="s">
         <v>12</v>
       </c>
       <c r="O5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
@@ -694,21 +734,27 @@
         <v>8</v>
       </c>
       <c r="N6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6" t="s">
+        <v>8</v>
+      </c>
+      <c r="R6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -717,10 +763,10 @@
         <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
         <v>8</v>
@@ -732,33 +778,39 @@
         <v>8</v>
       </c>
       <c r="J7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N7" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O7" t="s">
         <v>8</v>
       </c>
       <c r="P7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
@@ -767,10 +819,10 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
         <v>8</v>
@@ -782,19 +834,19 @@
         <v>8</v>
       </c>
       <c r="J8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8" t="s">
         <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O8" t="s">
         <v>8</v>
@@ -802,34 +854,40 @@
       <c r="P8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H9" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J9" t="s">
         <v>10</v>
@@ -838,42 +896,48 @@
         <v>10</v>
       </c>
       <c r="L9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M9" t="s">
         <v>8</v>
       </c>
       <c r="N9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H10" t="s">
         <v>12</v>
@@ -902,18 +966,30 @@
       <c r="P10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10" t="s">
+        <v>12</v>
+      </c>
+      <c r="R10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="N11" t="s">
-        <v>8</v>
+      <c r="B11" t="s">
+        <v>18</v>
       </c>
       <c r="O11" t="s">
         <v>8</v>
       </c>
       <c r="P11" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>8</v>
+      </c>
+      <c r="R11" t="s">
         <v>8</v>
       </c>
     </row>
@@ -982,51 +1058,51 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <f>_xlfn.IFS(Sheet1!B2="P", 5, Sheet1!B2="O", 3, Sheet1!B2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C2="P", 5, Sheet1!C2="O", 3, Sheet1!C2="A",0)</f>
         <v>5</v>
       </c>
       <c r="C2">
-        <f>_xlfn.IFS(Sheet1!C2="P", 5, Sheet1!C2="O", 3, Sheet1!C2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D2="P", 5, Sheet1!D2="O", 3, Sheet1!D2="A",0)</f>
         <v>5</v>
       </c>
       <c r="D2">
-        <f>_xlfn.IFS(Sheet1!D2="P", 5, Sheet1!D2="O", 3, Sheet1!D2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E2="P", 5, Sheet1!E2="O", 3, Sheet1!E2="A",0)</f>
         <v>5</v>
       </c>
       <c r="E2">
-        <f>_xlfn.IFS(Sheet1!E2="P", 5, Sheet1!E2="O", 3, Sheet1!E2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F2="P", 5, Sheet1!F2="O", 3, Sheet1!F2="A",0)</f>
         <v>5</v>
       </c>
       <c r="F2">
-        <f>_xlfn.IFS(Sheet1!F2="P", 5, Sheet1!F2="O", 3, Sheet1!F2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G2="P", 5, Sheet1!G2="O", 3, Sheet1!G2="A",0)</f>
         <v>5</v>
       </c>
       <c r="G2">
-        <f>_xlfn.IFS(Sheet1!G2="P", 5, Sheet1!G2="O", 3, Sheet1!G2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H2="P", 5, Sheet1!H2="O", 3, Sheet1!H2="A",0)</f>
         <v>3</v>
       </c>
       <c r="H2">
-        <f>_xlfn.IFS(Sheet1!H2="P", 5, Sheet1!H2="O", 3, Sheet1!H2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I2="P", 5, Sheet1!I2="O", 3, Sheet1!I2="A",0)</f>
         <v>5</v>
       </c>
       <c r="I2">
-        <f>_xlfn.IFS(Sheet1!I2="P", 5, Sheet1!I2="O", 3, Sheet1!I2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J2="P", 5, Sheet1!J2="O", 3, Sheet1!J2="A",0)</f>
         <v>5</v>
       </c>
       <c r="J2">
-        <f>_xlfn.IFS(Sheet1!J2="P", 5, Sheet1!J2="O", 3, Sheet1!J2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K2="P", 5, Sheet1!K2="O", 3, Sheet1!K2="A",0)</f>
         <v>0</v>
       </c>
       <c r="K2">
-        <f>_xlfn.IFS(Sheet1!K2="P", 5, Sheet1!K2="O", 3, Sheet1!K2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L2="P", 5, Sheet1!L2="O", 3, Sheet1!L2="A",0)</f>
         <v>0</v>
       </c>
       <c r="L2">
-        <f>_xlfn.IFS(Sheet1!L2="P", 5, Sheet1!L2="O", 3, Sheet1!L2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M2="P", 5, Sheet1!M2="O", 3, Sheet1!M2="A",0)</f>
         <v>5</v>
       </c>
       <c r="M2">
-        <f>_xlfn.IFS(Sheet1!M2="P", 5, Sheet1!M2="O", 3, Sheet1!M2="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N2="P", 5, Sheet1!N2="O", 3, Sheet1!N2="A",0)</f>
         <v>0</v>
       </c>
       <c r="N2">
@@ -1043,51 +1119,51 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <f>_xlfn.IFS(Sheet1!B3="P", 5, Sheet1!B3="O", 3, Sheet1!B3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C3="P", 5, Sheet1!C3="O", 3, Sheet1!C3="A",0)</f>
         <v>5</v>
       </c>
       <c r="C3">
-        <f>_xlfn.IFS(Sheet1!C3="P", 5, Sheet1!C3="O", 3, Sheet1!C3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D3="P", 5, Sheet1!D3="O", 3, Sheet1!D3="A",0)</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f>_xlfn.IFS(Sheet1!D3="P", 5, Sheet1!D3="O", 3, Sheet1!D3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E3="P", 5, Sheet1!E3="O", 3, Sheet1!E3="A",0)</f>
         <v>5</v>
       </c>
       <c r="E3">
-        <f>_xlfn.IFS(Sheet1!E3="P", 5, Sheet1!E3="O", 3, Sheet1!E3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F3="P", 5, Sheet1!F3="O", 3, Sheet1!F3="A",0)</f>
         <v>5</v>
       </c>
       <c r="F3">
-        <f>_xlfn.IFS(Sheet1!F3="P", 5, Sheet1!F3="O", 3, Sheet1!F3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G3="P", 5, Sheet1!G3="O", 3, Sheet1!G3="A",0)</f>
         <v>3</v>
       </c>
       <c r="G3">
-        <f>_xlfn.IFS(Sheet1!G3="P", 5, Sheet1!G3="O", 3, Sheet1!G3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H3="P", 5, Sheet1!H3="O", 3, Sheet1!H3="A",0)</f>
         <v>5</v>
       </c>
       <c r="H3">
-        <f>_xlfn.IFS(Sheet1!H3="P", 5, Sheet1!H3="O", 3, Sheet1!H3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I3="P", 5, Sheet1!I3="O", 3, Sheet1!I3="A",0)</f>
         <v>0</v>
       </c>
       <c r="I3">
-        <f>_xlfn.IFS(Sheet1!I3="P", 5, Sheet1!I3="O", 3, Sheet1!I3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J3="P", 5, Sheet1!J3="O", 3, Sheet1!J3="A",0)</f>
         <v>0</v>
       </c>
       <c r="J3">
-        <f>_xlfn.IFS(Sheet1!J3="P", 5, Sheet1!J3="O", 3, Sheet1!J3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K3="P", 5, Sheet1!K3="O", 3, Sheet1!K3="A",0)</f>
         <v>0</v>
       </c>
       <c r="K3">
-        <f>_xlfn.IFS(Sheet1!K3="P", 5, Sheet1!K3="O", 3, Sheet1!K3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L3="P", 5, Sheet1!L3="O", 3, Sheet1!L3="A",0)</f>
         <v>0</v>
       </c>
       <c r="L3">
-        <f>_xlfn.IFS(Sheet1!L3="P", 5, Sheet1!L3="O", 3, Sheet1!L3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M3="P", 5, Sheet1!M3="O", 3, Sheet1!M3="A",0)</f>
         <v>0</v>
       </c>
       <c r="M3">
-        <f>_xlfn.IFS(Sheet1!M3="P", 5, Sheet1!M3="O", 3, Sheet1!M3="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N3="P", 5, Sheet1!N3="O", 3, Sheet1!N3="A",0)</f>
         <v>5</v>
       </c>
       <c r="N3">
@@ -1104,51 +1180,51 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <f>_xlfn.IFS(Sheet1!B4="P", 5, Sheet1!B4="O", 3, Sheet1!B4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C4="P", 5, Sheet1!C4="O", 3, Sheet1!C4="A",0)</f>
         <v>5</v>
       </c>
       <c r="C4">
-        <f>_xlfn.IFS(Sheet1!C4="P", 5, Sheet1!C4="O", 3, Sheet1!C4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D4="P", 5, Sheet1!D4="O", 3, Sheet1!D4="A",0)</f>
         <v>5</v>
       </c>
       <c r="D4">
-        <f>_xlfn.IFS(Sheet1!D4="P", 5, Sheet1!D4="O", 3, Sheet1!D4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E4="P", 5, Sheet1!E4="O", 3, Sheet1!E4="A",0)</f>
         <v>5</v>
       </c>
       <c r="E4">
-        <f>_xlfn.IFS(Sheet1!E4="P", 5, Sheet1!E4="O", 3, Sheet1!E4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F4="P", 5, Sheet1!F4="O", 3, Sheet1!F4="A",0)</f>
         <v>0</v>
       </c>
       <c r="F4">
-        <f>_xlfn.IFS(Sheet1!F4="P", 5, Sheet1!F4="O", 3, Sheet1!F4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G4="P", 5, Sheet1!G4="O", 3, Sheet1!G4="A",0)</f>
         <v>3</v>
       </c>
       <c r="G4">
-        <f>_xlfn.IFS(Sheet1!G4="P", 5, Sheet1!G4="O", 3, Sheet1!G4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H4="P", 5, Sheet1!H4="O", 3, Sheet1!H4="A",0)</f>
         <v>5</v>
       </c>
       <c r="H4">
-        <f>_xlfn.IFS(Sheet1!H4="P", 5, Sheet1!H4="O", 3, Sheet1!H4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I4="P", 5, Sheet1!I4="O", 3, Sheet1!I4="A",0)</f>
         <v>5</v>
       </c>
       <c r="I4">
-        <f>_xlfn.IFS(Sheet1!I4="P", 5, Sheet1!I4="O", 3, Sheet1!I4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J4="P", 5, Sheet1!J4="O", 3, Sheet1!J4="A",0)</f>
         <v>0</v>
       </c>
       <c r="J4">
-        <f>_xlfn.IFS(Sheet1!J4="P", 5, Sheet1!J4="O", 3, Sheet1!J4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K4="P", 5, Sheet1!K4="O", 3, Sheet1!K4="A",0)</f>
         <v>5</v>
       </c>
       <c r="K4">
-        <f>_xlfn.IFS(Sheet1!K4="P", 5, Sheet1!K4="O", 3, Sheet1!K4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L4="P", 5, Sheet1!L4="O", 3, Sheet1!L4="A",0)</f>
         <v>5</v>
       </c>
       <c r="L4">
-        <f>_xlfn.IFS(Sheet1!L4="P", 5, Sheet1!L4="O", 3, Sheet1!L4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M4="P", 5, Sheet1!M4="O", 3, Sheet1!M4="A",0)</f>
         <v>5</v>
       </c>
       <c r="M4">
-        <f>_xlfn.IFS(Sheet1!M4="P", 5, Sheet1!M4="O", 3, Sheet1!M4="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N4="P", 5, Sheet1!N4="O", 3, Sheet1!N4="A",0)</f>
         <v>5</v>
       </c>
       <c r="N4">
@@ -1165,51 +1241,51 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <f>_xlfn.IFS(Sheet1!B5="P", 5, Sheet1!B5="O", 3, Sheet1!B5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C5="P", 5, Sheet1!C5="O", 3, Sheet1!C5="A",0)</f>
         <v>5</v>
       </c>
       <c r="C5">
-        <f>_xlfn.IFS(Sheet1!C5="P", 5, Sheet1!C5="O", 3, Sheet1!C5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D5="P", 5, Sheet1!D5="O", 3, Sheet1!D5="A",0)</f>
         <v>3</v>
       </c>
       <c r="D5">
-        <f>_xlfn.IFS(Sheet1!D5="P", 5, Sheet1!D5="O", 3, Sheet1!D5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E5="P", 5, Sheet1!E5="O", 3, Sheet1!E5="A",0)</f>
         <v>3</v>
       </c>
       <c r="E5">
-        <f>_xlfn.IFS(Sheet1!E5="P", 5, Sheet1!E5="O", 3, Sheet1!E5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F5="P", 5, Sheet1!F5="O", 3, Sheet1!F5="A",0)</f>
         <v>0</v>
       </c>
       <c r="F5">
-        <f>_xlfn.IFS(Sheet1!F5="P", 5, Sheet1!F5="O", 3, Sheet1!F5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G5="P", 5, Sheet1!G5="O", 3, Sheet1!G5="A",0)</f>
         <v>0</v>
       </c>
       <c r="G5">
-        <f>_xlfn.IFS(Sheet1!G5="P", 5, Sheet1!G5="O", 3, Sheet1!G5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H5="P", 5, Sheet1!H5="O", 3, Sheet1!H5="A",0)</f>
         <v>3</v>
       </c>
       <c r="H5">
-        <f>_xlfn.IFS(Sheet1!H5="P", 5, Sheet1!H5="O", 3, Sheet1!H5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I5="P", 5, Sheet1!I5="O", 3, Sheet1!I5="A",0)</f>
         <v>5</v>
       </c>
       <c r="I5">
-        <f>_xlfn.IFS(Sheet1!I5="P", 5, Sheet1!I5="O", 3, Sheet1!I5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J5="P", 5, Sheet1!J5="O", 3, Sheet1!J5="A",0)</f>
         <v>5</v>
       </c>
       <c r="J5">
-        <f>_xlfn.IFS(Sheet1!J5="P", 5, Sheet1!J5="O", 3, Sheet1!J5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K5="P", 5, Sheet1!K5="O", 3, Sheet1!K5="A",0)</f>
         <v>3</v>
       </c>
       <c r="K5">
-        <f>_xlfn.IFS(Sheet1!K5="P", 5, Sheet1!K5="O", 3, Sheet1!K5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L5="P", 5, Sheet1!L5="O", 3, Sheet1!L5="A",0)</f>
         <v>3</v>
       </c>
       <c r="L5">
-        <f>_xlfn.IFS(Sheet1!L5="P", 5, Sheet1!L5="O", 3, Sheet1!L5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M5="P", 5, Sheet1!M5="O", 3, Sheet1!M5="A",0)</f>
         <v>3</v>
       </c>
       <c r="M5">
-        <f>_xlfn.IFS(Sheet1!M5="P", 5, Sheet1!M5="O", 3, Sheet1!M5="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N5="P", 5, Sheet1!N5="O", 3, Sheet1!N5="A",0)</f>
         <v>0</v>
       </c>
       <c r="N5">
@@ -1226,51 +1302,51 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <f>_xlfn.IFS(Sheet1!B6="P", 5, Sheet1!B6="O", 3, Sheet1!B6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C6="P", 5, Sheet1!C6="O", 3, Sheet1!C6="A",0)</f>
         <v>5</v>
       </c>
       <c r="C6">
-        <f>_xlfn.IFS(Sheet1!C6="P", 5, Sheet1!C6="O", 3, Sheet1!C6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D6="P", 5, Sheet1!D6="O", 3, Sheet1!D6="A",0)</f>
         <v>5</v>
       </c>
       <c r="D6">
-        <f>_xlfn.IFS(Sheet1!D6="P", 5, Sheet1!D6="O", 3, Sheet1!D6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E6="P", 5, Sheet1!E6="O", 3, Sheet1!E6="A",0)</f>
         <v>5</v>
       </c>
       <c r="E6">
-        <f>_xlfn.IFS(Sheet1!E6="P", 5, Sheet1!E6="O", 3, Sheet1!E6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F6="P", 5, Sheet1!F6="O", 3, Sheet1!F6="A",0)</f>
         <v>5</v>
       </c>
       <c r="F6">
-        <f>_xlfn.IFS(Sheet1!F6="P", 5, Sheet1!F6="O", 3, Sheet1!F6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G6="P", 5, Sheet1!G6="O", 3, Sheet1!G6="A",0)</f>
         <v>5</v>
       </c>
       <c r="G6">
-        <f>_xlfn.IFS(Sheet1!G6="P", 5, Sheet1!G6="O", 3, Sheet1!G6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H6="P", 5, Sheet1!H6="O", 3, Sheet1!H6="A",0)</f>
         <v>5</v>
       </c>
       <c r="H6">
-        <f>_xlfn.IFS(Sheet1!H6="P", 5, Sheet1!H6="O", 3, Sheet1!H6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I6="P", 5, Sheet1!I6="O", 3, Sheet1!I6="A",0)</f>
         <v>5</v>
       </c>
       <c r="I6">
-        <f>_xlfn.IFS(Sheet1!I6="P", 5, Sheet1!I6="O", 3, Sheet1!I6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J6="P", 5, Sheet1!J6="O", 3, Sheet1!J6="A",0)</f>
         <v>5</v>
       </c>
       <c r="J6">
-        <f>_xlfn.IFS(Sheet1!J6="P", 5, Sheet1!J6="O", 3, Sheet1!J6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K6="P", 5, Sheet1!K6="O", 3, Sheet1!K6="A",0)</f>
         <v>5</v>
       </c>
       <c r="K6">
-        <f>_xlfn.IFS(Sheet1!K6="P", 5, Sheet1!K6="O", 3, Sheet1!K6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L6="P", 5, Sheet1!L6="O", 3, Sheet1!L6="A",0)</f>
         <v>5</v>
       </c>
       <c r="L6">
-        <f>_xlfn.IFS(Sheet1!L6="P", 5, Sheet1!L6="O", 3, Sheet1!L6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M6="P", 5, Sheet1!M6="O", 3, Sheet1!M6="A",0)</f>
         <v>5</v>
       </c>
       <c r="M6">
-        <f>_xlfn.IFS(Sheet1!M6="P", 5, Sheet1!M6="O", 3, Sheet1!M6="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N6="P", 5, Sheet1!N6="O", 3, Sheet1!N6="A",0)</f>
         <v>5</v>
       </c>
       <c r="N6">
@@ -1287,51 +1363,51 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <f>_xlfn.IFS(Sheet1!B7="P", 5, Sheet1!B7="O", 3, Sheet1!B7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C7="P", 5, Sheet1!C7="O", 3, Sheet1!C7="A",0)</f>
         <v>5</v>
       </c>
       <c r="C7">
-        <f>_xlfn.IFS(Sheet1!C7="P", 5, Sheet1!C7="O", 3, Sheet1!C7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D7="P", 5, Sheet1!D7="O", 3, Sheet1!D7="A",0)</f>
         <v>5</v>
       </c>
       <c r="D7">
-        <f>_xlfn.IFS(Sheet1!D7="P", 5, Sheet1!D7="O", 3, Sheet1!D7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E7="P", 5, Sheet1!E7="O", 3, Sheet1!E7="A",0)</f>
         <v>5</v>
       </c>
       <c r="E7">
-        <f>_xlfn.IFS(Sheet1!E7="P", 5, Sheet1!E7="O", 3, Sheet1!E7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F7="P", 5, Sheet1!F7="O", 3, Sheet1!F7="A",0)</f>
         <v>0</v>
       </c>
       <c r="F7">
-        <f>_xlfn.IFS(Sheet1!F7="P", 5, Sheet1!F7="O", 3, Sheet1!F7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G7="P", 5, Sheet1!G7="O", 3, Sheet1!G7="A",0)</f>
         <v>5</v>
       </c>
       <c r="G7">
-        <f>_xlfn.IFS(Sheet1!G7="P", 5, Sheet1!G7="O", 3, Sheet1!G7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H7="P", 5, Sheet1!H7="O", 3, Sheet1!H7="A",0)</f>
         <v>5</v>
       </c>
       <c r="H7">
-        <f>_xlfn.IFS(Sheet1!H7="P", 5, Sheet1!H7="O", 3, Sheet1!H7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I7="P", 5, Sheet1!I7="O", 3, Sheet1!I7="A",0)</f>
         <v>5</v>
       </c>
       <c r="I7">
-        <f>_xlfn.IFS(Sheet1!I7="P", 5, Sheet1!I7="O", 3, Sheet1!I7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J7="P", 5, Sheet1!J7="O", 3, Sheet1!J7="A",0)</f>
         <v>5</v>
       </c>
       <c r="J7">
-        <f>_xlfn.IFS(Sheet1!J7="P", 5, Sheet1!J7="O", 3, Sheet1!J7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K7="P", 5, Sheet1!K7="O", 3, Sheet1!K7="A",0)</f>
         <v>3</v>
       </c>
       <c r="K7">
-        <f>_xlfn.IFS(Sheet1!K7="P", 5, Sheet1!K7="O", 3, Sheet1!K7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L7="P", 5, Sheet1!L7="O", 3, Sheet1!L7="A",0)</f>
         <v>0</v>
       </c>
       <c r="L7">
-        <f>_xlfn.IFS(Sheet1!L7="P", 5, Sheet1!L7="O", 3, Sheet1!L7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M7="P", 5, Sheet1!M7="O", 3, Sheet1!M7="A",0)</f>
         <v>5</v>
       </c>
       <c r="M7">
-        <f>_xlfn.IFS(Sheet1!M7="P", 5, Sheet1!M7="O", 3, Sheet1!M7="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N7="P", 5, Sheet1!N7="O", 3, Sheet1!N7="A",0)</f>
         <v>0</v>
       </c>
       <c r="N7">
@@ -1348,51 +1424,51 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <f>_xlfn.IFS(Sheet1!B8="P", 5, Sheet1!B8="O", 3, Sheet1!B8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C8="P", 5, Sheet1!C8="O", 3, Sheet1!C8="A",0)</f>
         <v>5</v>
       </c>
       <c r="C8">
-        <f>_xlfn.IFS(Sheet1!C8="P", 5, Sheet1!C8="O", 3, Sheet1!C8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D8="P", 5, Sheet1!D8="O", 3, Sheet1!D8="A",0)</f>
         <v>5</v>
       </c>
       <c r="D8">
-        <f>_xlfn.IFS(Sheet1!D8="P", 5, Sheet1!D8="O", 3, Sheet1!D8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E8="P", 5, Sheet1!E8="O", 3, Sheet1!E8="A",0)</f>
         <v>5</v>
       </c>
       <c r="E8">
-        <f>_xlfn.IFS(Sheet1!E8="P", 5, Sheet1!E8="O", 3, Sheet1!E8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F8="P", 5, Sheet1!F8="O", 3, Sheet1!F8="A",0)</f>
         <v>0</v>
       </c>
       <c r="F8">
-        <f>_xlfn.IFS(Sheet1!F8="P", 5, Sheet1!F8="O", 3, Sheet1!F8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G8="P", 5, Sheet1!G8="O", 3, Sheet1!G8="A",0)</f>
         <v>5</v>
       </c>
       <c r="G8">
-        <f>_xlfn.IFS(Sheet1!G8="P", 5, Sheet1!G8="O", 3, Sheet1!G8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H8="P", 5, Sheet1!H8="O", 3, Sheet1!H8="A",0)</f>
         <v>5</v>
       </c>
       <c r="H8">
-        <f>_xlfn.IFS(Sheet1!H8="P", 5, Sheet1!H8="O", 3, Sheet1!H8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I8="P", 5, Sheet1!I8="O", 3, Sheet1!I8="A",0)</f>
         <v>5</v>
       </c>
       <c r="I8">
-        <f>_xlfn.IFS(Sheet1!I8="P", 5, Sheet1!I8="O", 3, Sheet1!I8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J8="P", 5, Sheet1!J8="O", 3, Sheet1!J8="A",0)</f>
         <v>5</v>
       </c>
       <c r="J8">
-        <f>_xlfn.IFS(Sheet1!J8="P", 5, Sheet1!J8="O", 3, Sheet1!J8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K8="P", 5, Sheet1!K8="O", 3, Sheet1!K8="A",0)</f>
         <v>3</v>
       </c>
       <c r="K8">
-        <f>_xlfn.IFS(Sheet1!K8="P", 5, Sheet1!K8="O", 3, Sheet1!K8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L8="P", 5, Sheet1!L8="O", 3, Sheet1!L8="A",0)</f>
         <v>3</v>
       </c>
       <c r="L8">
-        <f>_xlfn.IFS(Sheet1!L8="P", 5, Sheet1!L8="O", 3, Sheet1!L8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M8="P", 5, Sheet1!M8="O", 3, Sheet1!M8="A",0)</f>
         <v>5</v>
       </c>
       <c r="M8">
-        <f>_xlfn.IFS(Sheet1!M8="P", 5, Sheet1!M8="O", 3, Sheet1!M8="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N8="P", 5, Sheet1!N8="O", 3, Sheet1!N8="A",0)</f>
         <v>0</v>
       </c>
       <c r="N8">
@@ -1409,51 +1485,51 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <f>_xlfn.IFS(Sheet1!B9="P", 5, Sheet1!B9="O", 3, Sheet1!B9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C9="P", 5, Sheet1!C9="O", 3, Sheet1!C9="A",0)</f>
         <v>3</v>
       </c>
       <c r="C9">
-        <f>_xlfn.IFS(Sheet1!C9="P", 5, Sheet1!C9="O", 3, Sheet1!C9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D9="P", 5, Sheet1!D9="O", 3, Sheet1!D9="A",0)</f>
         <v>3</v>
       </c>
       <c r="D9">
-        <f>_xlfn.IFS(Sheet1!D9="P", 5, Sheet1!D9="O", 3, Sheet1!D9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E9="P", 5, Sheet1!E9="O", 3, Sheet1!E9="A",0)</f>
         <v>5</v>
       </c>
       <c r="E9">
-        <f>_xlfn.IFS(Sheet1!E9="P", 5, Sheet1!E9="O", 3, Sheet1!E9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F9="P", 5, Sheet1!F9="O", 3, Sheet1!F9="A",0)</f>
         <v>5</v>
       </c>
       <c r="F9">
-        <f>_xlfn.IFS(Sheet1!F9="P", 5, Sheet1!F9="O", 3, Sheet1!F9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G9="P", 5, Sheet1!G9="O", 3, Sheet1!G9="A",0)</f>
         <v>3</v>
       </c>
       <c r="G9">
-        <f>_xlfn.IFS(Sheet1!G9="P", 5, Sheet1!G9="O", 3, Sheet1!G9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H9="P", 5, Sheet1!H9="O", 3, Sheet1!H9="A",0)</f>
         <v>0</v>
       </c>
       <c r="H9">
-        <f>_xlfn.IFS(Sheet1!H9="P", 5, Sheet1!H9="O", 3, Sheet1!H9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I9="P", 5, Sheet1!I9="O", 3, Sheet1!I9="A",0)</f>
         <v>5</v>
       </c>
       <c r="I9">
-        <f>_xlfn.IFS(Sheet1!I9="P", 5, Sheet1!I9="O", 3, Sheet1!I9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J9="P", 5, Sheet1!J9="O", 3, Sheet1!J9="A",0)</f>
         <v>3</v>
       </c>
       <c r="J9">
-        <f>_xlfn.IFS(Sheet1!J9="P", 5, Sheet1!J9="O", 3, Sheet1!J9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K9="P", 5, Sheet1!K9="O", 3, Sheet1!K9="A",0)</f>
         <v>3</v>
       </c>
       <c r="K9">
-        <f>_xlfn.IFS(Sheet1!K9="P", 5, Sheet1!K9="O", 3, Sheet1!K9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L9="P", 5, Sheet1!L9="O", 3, Sheet1!L9="A",0)</f>
         <v>3</v>
       </c>
       <c r="L9">
-        <f>_xlfn.IFS(Sheet1!L9="P", 5, Sheet1!L9="O", 3, Sheet1!L9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M9="P", 5, Sheet1!M9="O", 3, Sheet1!M9="A",0)</f>
         <v>5</v>
       </c>
       <c r="M9">
-        <f>_xlfn.IFS(Sheet1!M9="P", 5, Sheet1!M9="O", 3, Sheet1!M9="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N9="P", 5, Sheet1!N9="O", 3, Sheet1!N9="A",0)</f>
         <v>5</v>
       </c>
       <c r="N9">
@@ -1470,51 +1546,51 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <f>_xlfn.IFS(Sheet1!B10="P", 5, Sheet1!B10="O", 3, Sheet1!B10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!C10="P", 5, Sheet1!C10="O", 3, Sheet1!C10="A",0)</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>_xlfn.IFS(Sheet1!C10="P", 5, Sheet1!C10="O", 3, Sheet1!C10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!D10="P", 5, Sheet1!D10="O", 3, Sheet1!D10="A",0)</f>
         <v>5</v>
       </c>
       <c r="D10">
-        <f>_xlfn.IFS(Sheet1!D10="P", 5, Sheet1!D10="O", 3, Sheet1!D10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!E10="P", 5, Sheet1!E10="O", 3, Sheet1!E10="A",0)</f>
         <v>5</v>
       </c>
       <c r="E10">
-        <f>_xlfn.IFS(Sheet1!E10="P", 5, Sheet1!E10="O", 3, Sheet1!E10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!F10="P", 5, Sheet1!F10="O", 3, Sheet1!F10="A",0)</f>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>_xlfn.IFS(Sheet1!F10="P", 5, Sheet1!F10="O", 3, Sheet1!F10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!G10="P", 5, Sheet1!G10="O", 3, Sheet1!G10="A",0)</f>
         <v>5</v>
       </c>
       <c r="G10">
-        <f>_xlfn.IFS(Sheet1!G10="P", 5, Sheet1!G10="O", 3, Sheet1!G10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!H10="P", 5, Sheet1!H10="O", 3, Sheet1!H10="A",0)</f>
         <v>0</v>
       </c>
       <c r="H10">
-        <f>_xlfn.IFS(Sheet1!H10="P", 5, Sheet1!H10="O", 3, Sheet1!H10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!I10="P", 5, Sheet1!I10="O", 3, Sheet1!I10="A",0)</f>
         <v>0</v>
       </c>
       <c r="I10">
-        <f>_xlfn.IFS(Sheet1!I10="P", 5, Sheet1!I10="O", 3, Sheet1!I10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!J10="P", 5, Sheet1!J10="O", 3, Sheet1!J10="A",0)</f>
         <v>0</v>
       </c>
       <c r="J10">
-        <f>_xlfn.IFS(Sheet1!J10="P", 5, Sheet1!J10="O", 3, Sheet1!J10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!K10="P", 5, Sheet1!K10="O", 3, Sheet1!K10="A",0)</f>
         <v>0</v>
       </c>
       <c r="K10">
-        <f>_xlfn.IFS(Sheet1!K10="P", 5, Sheet1!K10="O", 3, Sheet1!K10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!L10="P", 5, Sheet1!L10="O", 3, Sheet1!L10="A",0)</f>
         <v>0</v>
       </c>
       <c r="L10">
-        <f>_xlfn.IFS(Sheet1!L10="P", 5, Sheet1!L10="O", 3, Sheet1!L10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!M10="P", 5, Sheet1!M10="O", 3, Sheet1!M10="A",0)</f>
         <v>0</v>
       </c>
       <c r="M10">
-        <f>_xlfn.IFS(Sheet1!M10="P", 5, Sheet1!M10="O", 3, Sheet1!M10="A",0)</f>
+        <f>_xlfn.IFS(Sheet1!N10="P", 5, Sheet1!N10="O", 3, Sheet1!N10="A",0)</f>
         <v>0</v>
       </c>
       <c r="N10">

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D095CB3B-396F-463D-AEAA-E41B0B4FAAA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF30EF69-88B9-45D3-BDA5-956A45F710F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -413,7 +413,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -468,8 +468,11 @@
       <c r="R1" s="1">
         <v>45626</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S1" s="1">
+        <v>45633</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -524,8 +527,11 @@
       <c r="R2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -580,8 +586,11 @@
       <c r="R3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -636,8 +645,11 @@
       <c r="R4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -692,8 +704,11 @@
       <c r="R5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -748,8 +763,11 @@
       <c r="R6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -804,8 +822,11 @@
       <c r="R7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -860,8 +881,11 @@
       <c r="R8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -916,8 +940,11 @@
       <c r="R9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -972,8 +999,11 @@
       <c r="R10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="S10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -990,6 +1020,9 @@
         <v>8</v>
       </c>
       <c r="R11" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF30EF69-88B9-45D3-BDA5-956A45F710F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE934B7-8F72-4075-BEBC-B4EA59EDBA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -413,7 +413,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -471,8 +471,11 @@
       <c r="S1" s="1">
         <v>45633</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T1" s="1">
+        <v>45640</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -530,8 +533,11 @@
       <c r="S2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -589,8 +595,11 @@
       <c r="S3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -648,8 +657,11 @@
       <c r="S4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -707,8 +719,11 @@
       <c r="S5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -766,8 +781,11 @@
       <c r="S6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -825,8 +843,11 @@
       <c r="S7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -884,8 +905,11 @@
       <c r="S8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -943,8 +967,11 @@
       <c r="S9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1002,8 +1029,11 @@
       <c r="S10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="T10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1023,6 +1053,9 @@
         <v>8</v>
       </c>
       <c r="S11" t="s">
+        <v>8</v>
+      </c>
+      <c r="T11" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE934B7-8F72-4075-BEBC-B4EA59EDBA20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E492E4-CAC1-43EC-863D-3875090E44F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -413,7 +413,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -474,8 +474,11 @@
       <c r="T1" s="1">
         <v>45640</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U1" s="1">
+        <v>45647</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -536,8 +539,11 @@
       <c r="T2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -598,8 +604,11 @@
       <c r="T3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -660,8 +669,11 @@
       <c r="T4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -722,8 +734,11 @@
       <c r="T5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -784,8 +799,11 @@
       <c r="T6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -846,8 +864,11 @@
       <c r="T7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -908,8 +929,11 @@
       <c r="T8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -970,8 +994,11 @@
       <c r="T9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1032,8 +1059,11 @@
       <c r="T10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1056,6 +1086,9 @@
         <v>8</v>
       </c>
       <c r="T11" t="s">
+        <v>8</v>
+      </c>
+      <c r="U11" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1E492E4-CAC1-43EC-863D-3875090E44F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D1F35C-9B66-49C7-A4FC-DB7BA9120586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Attendance" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -400,8 +401,830 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>45500</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>45507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>45514</v>
+      </c>
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>45521</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>45528</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>45535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>45542</v>
+      </c>
+      <c r="B13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>45549</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>45565</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>45572</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>45577</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>45584</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>45591</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" t="s">
+        <v>12</v>
+      </c>
+      <c r="K21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>45605</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" t="s">
+        <v>12</v>
+      </c>
+      <c r="K24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>45612</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" t="s">
+        <v>12</v>
+      </c>
+      <c r="K25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>45626</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" t="s">
+        <v>10</v>
+      </c>
+      <c r="J26" t="s">
+        <v>12</v>
+      </c>
+      <c r="K26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>45633</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>45640</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" t="s">
+        <v>12</v>
+      </c>
+      <c r="K30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="1">
+        <v>45647</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" t="s">
+        <v>10</v>
+      </c>
+      <c r="I31" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" t="s">
+        <v>12</v>
+      </c>
+      <c r="K31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="1">
+        <v>45654</v>
+      </c>
+      <c r="B32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" t="s">
+        <v>12</v>
+      </c>
+      <c r="K32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="1">
+        <v>45661</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" t="s">
+        <v>8</v>
+      </c>
+      <c r="H34" t="s">
+        <v>8</v>
+      </c>
+      <c r="I34" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34" t="s">
+        <v>12</v>
+      </c>
+      <c r="K34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.88671875" bestFit="1" customWidth="1"/>
@@ -413,7 +1236,7 @@
     <col min="10" max="10" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -477,8 +1300,11 @@
       <c r="U1" s="1">
         <v>45647</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" s="1">
+        <v>45654</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -542,8 +1368,11 @@
       <c r="U2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -607,8 +1436,11 @@
       <c r="U3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -672,8 +1504,11 @@
       <c r="U4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -737,8 +1572,11 @@
       <c r="U5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -802,8 +1640,11 @@
       <c r="U6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -867,8 +1708,11 @@
       <c r="U7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -932,8 +1776,11 @@
       <c r="U8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -997,8 +1844,11 @@
       <c r="U9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1062,8 +1912,11 @@
       <c r="U10" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1090,6 +1943,9 @@
       </c>
       <c r="U11" t="s">
         <v>8</v>
+      </c>
+      <c r="V11" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0024F37A-C562-416B-828F-1FBDF4D4E931}">
   <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D1F35C-9B66-49C7-A4FC-DB7BA9120586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5648F831-900C-441C-ACEC-D7A7ABEFA00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1214,6 +1214,41 @@
         <v>12</v>
       </c>
       <c r="K34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="1">
+        <v>45675</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" t="s">
+        <v>12</v>
+      </c>
+      <c r="J35" t="s">
+        <v>12</v>
+      </c>
+      <c r="K35" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5648F831-900C-441C-ACEC-D7A7ABEFA00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DB8E0E-EC17-4D90-BA27-01A5550843CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1249,6 +1249,41 @@
         <v>12</v>
       </c>
       <c r="K35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="1">
+        <v>45682</v>
+      </c>
+      <c r="B36" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" t="s">
+        <v>8</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
+      </c>
+      <c r="I36" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" t="s">
+        <v>12</v>
+      </c>
+      <c r="K36" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DB8E0E-EC17-4D90-BA27-01A5550843CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A84E70C-705C-4A2E-B528-A810024E2DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1284,6 +1284,41 @@
         <v>12</v>
       </c>
       <c r="K36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="1">
+        <v>45689</v>
+      </c>
+      <c r="B38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>8</v>
+      </c>
+      <c r="H38" t="s">
+        <v>8</v>
+      </c>
+      <c r="I38" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" t="s">
+        <v>12</v>
+      </c>
+      <c r="K38" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A84E70C-705C-4A2E-B528-A810024E2DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDC7214-811C-4E50-BE25-39834A879C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1320,6 +1320,41 @@
       </c>
       <c r="K38" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="1">
+        <v>45696</v>
+      </c>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39" t="s">
+        <v>8</v>
+      </c>
+      <c r="I39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J39" t="s">
+        <v>12</v>
+      </c>
+      <c r="K39" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDC7214-811C-4E50-BE25-39834A879C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9933883D-96F7-4A3B-84E7-5E4ADE671689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1355,6 +1355,41 @@
       </c>
       <c r="K39" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="1">
+        <v>45703</v>
+      </c>
+      <c r="B40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" t="s">
+        <v>8</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
+      </c>
+      <c r="I40" t="s">
+        <v>8</v>
+      </c>
+      <c r="J40" t="s">
+        <v>12</v>
+      </c>
+      <c r="K40" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9933883D-96F7-4A3B-84E7-5E4ADE671689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97481A01-D36E-43F3-8AB8-CD4F40168A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1389,6 +1389,41 @@
         <v>12</v>
       </c>
       <c r="K40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="1">
+        <v>45717</v>
+      </c>
+      <c r="B42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" t="s">
+        <v>12</v>
+      </c>
+      <c r="I42" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" t="s">
+        <v>12</v>
+      </c>
+      <c r="K42" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97481A01-D36E-43F3-8AB8-CD4F40168A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A90D253-9321-4229-9F40-C697DD979079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -84,6 +84,9 @@
   </si>
   <si>
     <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Dhruvi Desai</t>
   </si>
 </sst>
 </file>
@@ -402,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -450,7 +453,7 @@
         <v>11</v>
       </c>
       <c r="K1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1424,6 +1427,76 @@
         <v>12</v>
       </c>
       <c r="K42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="1">
+        <v>45724</v>
+      </c>
+      <c r="B43" t="s">
+        <v>12</v>
+      </c>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" t="s">
+        <v>12</v>
+      </c>
+      <c r="K43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="1">
+        <v>45731</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" t="s">
+        <v>12</v>
+      </c>
+      <c r="K44" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A90D253-9321-4229-9F40-C697DD979079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C365A4-2501-4799-A03B-233CC723FAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -405,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -417,11 +417,10 @@
     <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,13 +449,10 @@
         <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -485,13 +481,10 @@
         <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45500</v>
       </c>
@@ -519,17 +512,14 @@
       <c r="I3" t="s">
         <v>10</v>
       </c>
-      <c r="J3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45507</v>
       </c>
@@ -557,11 +547,8 @@
       <c r="I6" t="s">
         <v>10</v>
       </c>
-      <c r="J6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45514</v>
       </c>
@@ -589,11 +576,8 @@
       <c r="I7" t="s">
         <v>8</v>
       </c>
-      <c r="J7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45521</v>
       </c>
@@ -621,11 +605,8 @@
       <c r="I8" t="s">
         <v>8</v>
       </c>
-      <c r="J8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45528</v>
       </c>
@@ -653,11 +634,8 @@
       <c r="I9" t="s">
         <v>10</v>
       </c>
-      <c r="J9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45535</v>
       </c>
@@ -685,17 +663,14 @@
       <c r="I10" t="s">
         <v>12</v>
       </c>
-      <c r="J10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45542</v>
       </c>
@@ -723,11 +698,8 @@
       <c r="I13" t="s">
         <v>8</v>
       </c>
-      <c r="J13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45549</v>
       </c>
@@ -755,11 +727,8 @@
       <c r="I14" t="s">
         <v>10</v>
       </c>
-      <c r="J14" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45565</v>
       </c>
@@ -787,17 +756,14 @@
       <c r="I15" t="s">
         <v>10</v>
       </c>
-      <c r="J15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45572</v>
       </c>
@@ -825,11 +791,8 @@
       <c r="I18" t="s">
         <v>10</v>
       </c>
-      <c r="J18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45577</v>
       </c>
@@ -857,11 +820,8 @@
       <c r="I19" t="s">
         <v>8</v>
       </c>
-      <c r="J19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45584</v>
       </c>
@@ -889,11 +849,8 @@
       <c r="I20" t="s">
         <v>8</v>
       </c>
-      <c r="J20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45591</v>
       </c>
@@ -922,19 +879,16 @@
         <v>10</v>
       </c>
       <c r="J21" t="s">
-        <v>12</v>
-      </c>
-      <c r="K21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45605</v>
       </c>
@@ -963,13 +917,10 @@
         <v>12</v>
       </c>
       <c r="J24" t="s">
-        <v>12</v>
-      </c>
-      <c r="K24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45612</v>
       </c>
@@ -998,13 +949,10 @@
         <v>8</v>
       </c>
       <c r="J25" t="s">
-        <v>12</v>
-      </c>
-      <c r="K25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>45626</v>
       </c>
@@ -1033,19 +981,16 @@
         <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>12</v>
-      </c>
-      <c r="K26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>45633</v>
       </c>
@@ -1074,13 +1019,10 @@
         <v>8</v>
       </c>
       <c r="J29" t="s">
-        <v>12</v>
-      </c>
-      <c r="K29" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45640</v>
       </c>
@@ -1109,13 +1051,10 @@
         <v>8</v>
       </c>
       <c r="J30" t="s">
-        <v>12</v>
-      </c>
-      <c r="K30" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45647</v>
       </c>
@@ -1144,13 +1083,10 @@
         <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>12</v>
-      </c>
-      <c r="K31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45654</v>
       </c>
@@ -1181,11 +1117,8 @@
       <c r="J32" t="s">
         <v>12</v>
       </c>
-      <c r="K32" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45661</v>
       </c>
@@ -1214,13 +1147,10 @@
         <v>10</v>
       </c>
       <c r="J34" t="s">
-        <v>12</v>
-      </c>
-      <c r="K34" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45675</v>
       </c>
@@ -1249,13 +1179,10 @@
         <v>12</v>
       </c>
       <c r="J35" t="s">
-        <v>12</v>
-      </c>
-      <c r="K35" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45682</v>
       </c>
@@ -1284,13 +1211,10 @@
         <v>8</v>
       </c>
       <c r="J36" t="s">
-        <v>12</v>
-      </c>
-      <c r="K36" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45689</v>
       </c>
@@ -1319,13 +1243,10 @@
         <v>8</v>
       </c>
       <c r="J38" t="s">
-        <v>12</v>
-      </c>
-      <c r="K38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45696</v>
       </c>
@@ -1356,11 +1277,8 @@
       <c r="J39" t="s">
         <v>12</v>
       </c>
-      <c r="K39" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45703</v>
       </c>
@@ -1389,13 +1307,10 @@
         <v>8</v>
       </c>
       <c r="J40" t="s">
-        <v>12</v>
-      </c>
-      <c r="K40" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45717</v>
       </c>
@@ -1424,13 +1339,10 @@
         <v>8</v>
       </c>
       <c r="J42" t="s">
-        <v>12</v>
-      </c>
-      <c r="K42" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45724</v>
       </c>
@@ -1461,11 +1373,8 @@
       <c r="J43" t="s">
         <v>12</v>
       </c>
-      <c r="K43" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45731</v>
       </c>
@@ -1494,9 +1403,38 @@
         <v>10</v>
       </c>
       <c r="J44" t="s">
-        <v>12</v>
-      </c>
-      <c r="K44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="1">
+        <v>45738</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C365A4-2501-4799-A03B-233CC723FAD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1DD9E5-C26B-4943-BD0E-73069157360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -405,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1435,6 +1435,38 @@
         <v>8</v>
       </c>
       <c r="J45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="1">
+        <v>45745</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D1DD9E5-C26B-4943-BD0E-73069157360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DF7AC6-A94E-46C1-8CAD-04F4650142B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>Dhruvi Desai</t>
+  </si>
+  <si>
+    <t>Vrund Patel</t>
+  </si>
+  <si>
+    <t>Ivanshi Thakkar</t>
   </si>
 </sst>
 </file>
@@ -405,7 +411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -418,9 +424,11 @@
     <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,8 +459,14 @@
       <c r="J1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -483,8 +497,14 @@
       <c r="J2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45500</v>
       </c>
@@ -513,13 +533,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45507</v>
       </c>
@@ -548,7 +568,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45514</v>
       </c>
@@ -577,7 +597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45521</v>
       </c>
@@ -606,7 +626,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45528</v>
       </c>
@@ -635,7 +655,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45535</v>
       </c>
@@ -664,13 +684,13 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45542</v>
       </c>
@@ -699,7 +719,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45549</v>
       </c>
@@ -728,7 +748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45565</v>
       </c>
@@ -757,7 +777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -1467,6 +1487,44 @@
         <v>8</v>
       </c>
       <c r="J46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="1">
+        <v>45752</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" t="s">
+        <v>12</v>
+      </c>
+      <c r="K49" t="s">
+        <v>8</v>
+      </c>
+      <c r="L49" t="s">
         <v>8</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRClub/Attendance.xlsx
+++ b/2024AIDataScienceGNRClub/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRClub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DF7AC6-A94E-46C1-8CAD-04F4650142B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC337389-7069-4F56-A0FD-092514712BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="23">
   <si>
     <t>Name</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Ivanshi Thakkar</t>
+  </si>
+  <si>
+    <t>Removed</t>
   </si>
 </sst>
 </file>
@@ -411,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EB1B165-9200-4089-B05B-75C13E96CEAA}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -1526,6 +1529,44 @@
       </c>
       <c r="L49" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="1">
+        <v>45759</v>
+      </c>
+      <c r="B50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" t="s">
+        <v>10</v>
+      </c>
+      <c r="G50" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" t="s">
+        <v>12</v>
+      </c>
+      <c r="J50" t="s">
+        <v>10</v>
+      </c>
+      <c r="K50" t="s">
+        <v>10</v>
+      </c>
+      <c r="L50" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
